--- a/artfynd/A 26446-2025 artfynd.xlsx
+++ b/artfynd/A 26446-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100350471</v>
+        <v>100350470</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549212.8748899817</v>
+        <v>549291</v>
       </c>
       <c r="R2" t="n">
-        <v>6901201.593993583</v>
+        <v>6901161</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100350112</v>
+        <v>100350471</v>
       </c>
       <c r="B3" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549080.2038986838</v>
+        <v>549213</v>
       </c>
       <c r="R3" t="n">
-        <v>6901334.851212583</v>
+        <v>6901201</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100350159</v>
+        <v>100350112</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549276.7139589223</v>
+        <v>549080</v>
       </c>
       <c r="R4" t="n">
-        <v>6901114.415379629</v>
+        <v>6901335</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,58 +978,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100349993</v>
+        <v>100350028</v>
       </c>
       <c r="B5" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björntjärnsberget, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549062.8157938047</v>
+        <v>549298</v>
       </c>
       <c r="R5" t="n">
-        <v>6901278.655356771</v>
+        <v>6901152</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,19 +1046,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,6 +1072,415 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>99444641</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björntjärnsberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>549224</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6901413</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ursula Zinko</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ursula Zinko</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100349993</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björntjärnsberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>549063</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6901278</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-09-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-09-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>99444640</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björntjärnsberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>549288</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6901373</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ursula Zinko</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ursula Zinko</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100350159</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Björntjärnsberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>549277</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6901114</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-09-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-09-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 26446-2025 artfynd.xlsx
+++ b/artfynd/A 26446-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100350470</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100350471</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100350112</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100350028</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99444641</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100349993</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99444640</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,8 +1525,23 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100350159</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>